--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244213</v>
+        <v>131244111</v>
       </c>
       <c r="B2" t="n">
-        <v>91805</v>
+        <v>79244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447044</v>
+        <v>446673</v>
       </c>
       <c r="R2" t="n">
-        <v>7000989</v>
+        <v>7000892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +755,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,9 +785,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>91805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,28 +821,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R3" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +890,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,14 +915,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>91805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R2" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +755,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -785,14 +780,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244213</v>
+        <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>91805</v>
+        <v>79244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,28 +811,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447044</v>
+        <v>446673</v>
       </c>
       <c r="R3" t="n">
-        <v>7000989</v>
+        <v>7000892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,6 +880,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -915,9 +910,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244217</v>
+        <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,37 +2087,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447029</v>
+        <v>446792</v>
       </c>
       <c r="R13" t="n">
-        <v>7000963</v>
+        <v>7001280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,28 +2171,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2197,10 +2194,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131244189</v>
+        <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>58043</v>
+        <v>79244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,50 +2205,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446792</v>
+        <v>447029</v>
       </c>
       <c r="R14" t="n">
-        <v>7001280</v>
+        <v>7000963</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,12 +2276,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131244211</v>
+        <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,50 +1081,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446698</v>
+        <v>447044</v>
       </c>
       <c r="R5" t="n">
-        <v>7000864</v>
+        <v>7000989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,6 +1152,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,9 +1161,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1193,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244216</v>
+        <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,37 +1202,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447044</v>
+        <v>446698</v>
       </c>
       <c r="R6" t="n">
-        <v>7000989</v>
+        <v>7000864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1286,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1284,19 +1294,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244189</v>
+        <v>131244217</v>
       </c>
       <c r="B13" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,50 +2087,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446792</v>
+        <v>447029</v>
       </c>
       <c r="R13" t="n">
-        <v>7001280</v>
+        <v>7000963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2171,12 +2158,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2194,10 +2197,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131244217</v>
+        <v>131244189</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,37 +2208,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447029</v>
+        <v>446792</v>
       </c>
       <c r="R14" t="n">
-        <v>7000963</v>
+        <v>7001280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2276,28 +2292,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244213</v>
+        <v>131244111</v>
       </c>
       <c r="B2" t="n">
-        <v>91806</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447044</v>
+        <v>446673</v>
       </c>
       <c r="R2" t="n">
-        <v>7000989</v>
+        <v>7000892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +755,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,9 +785,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244111</v>
+        <v>131244108</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,28 +821,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446673</v>
+        <v>446594</v>
       </c>
       <c r="R3" t="n">
-        <v>7000892</v>
+        <v>7000953</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,13 +902,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -912,12 +922,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244108</v>
+        <v>131244213</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91806</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,29 +956,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -978,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446594</v>
+        <v>447044</v>
       </c>
       <c r="R4" t="n">
-        <v>7000953</v>
+        <v>7000989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,23 +1025,19 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1045,14 +1050,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131244216</v>
+        <v>131244211</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,37 +1081,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447044</v>
+        <v>446698</v>
       </c>
       <c r="R5" t="n">
-        <v>7000989</v>
+        <v>7000864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,7 +1165,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1161,19 +1173,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1191,10 +1193,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244211</v>
+        <v>131244216</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,50 +1204,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446698</v>
+        <v>447044</v>
       </c>
       <c r="R6" t="n">
-        <v>7000864</v>
+        <v>7000989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,6 +1275,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1294,9 +1284,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>91806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R2" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +755,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -785,14 +780,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244108</v>
+        <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,29 +811,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446594</v>
+        <v>446673</v>
       </c>
       <c r="R3" t="n">
-        <v>7000953</v>
+        <v>7000892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +891,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -922,12 +912,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244213</v>
+        <v>131244108</v>
       </c>
       <c r="B4" t="n">
-        <v>91806</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,28 +946,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -987,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447044</v>
+        <v>446594</v>
       </c>
       <c r="R4" t="n">
-        <v>7000989</v>
+        <v>7000953</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,19 +1016,23 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1050,9 +1045,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244217</v>
+        <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,37 +2087,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447029</v>
+        <v>446792</v>
       </c>
       <c r="R13" t="n">
-        <v>7000963</v>
+        <v>7001280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,28 +2171,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2197,10 +2194,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131244189</v>
+        <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,50 +2205,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446792</v>
+        <v>447029</v>
       </c>
       <c r="R14" t="n">
-        <v>7001280</v>
+        <v>7000963</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,12 +2276,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131244211</v>
+        <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,50 +1081,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446698</v>
+        <v>447044</v>
       </c>
       <c r="R5" t="n">
-        <v>7000864</v>
+        <v>7000989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,6 +1152,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,9 +1161,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1193,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244216</v>
+        <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,37 +1202,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447044</v>
+        <v>446698</v>
       </c>
       <c r="R6" t="n">
-        <v>7000989</v>
+        <v>7000864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1286,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1284,19 +1294,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244213</v>
+        <v>131244108</v>
       </c>
       <c r="B2" t="n">
-        <v>91810</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447044</v>
+        <v>446594</v>
       </c>
       <c r="R2" t="n">
-        <v>7000989</v>
+        <v>7000953</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,19 +756,23 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -780,9 +785,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>91812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,28 +821,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R3" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +890,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,14 +915,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244108</v>
+        <v>131244111</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,29 +946,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -978,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446594</v>
+        <v>446673</v>
       </c>
       <c r="R4" t="n">
-        <v>7000953</v>
+        <v>7000892</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1017,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,12 +1026,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131244216</v>
+        <v>131244211</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>58045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,37 +1081,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447044</v>
+        <v>446698</v>
       </c>
       <c r="R5" t="n">
-        <v>7000989</v>
+        <v>7000864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,7 +1165,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1161,19 +1173,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1191,10 +1193,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244211</v>
+        <v>131244216</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,50 +1204,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446698</v>
+        <v>447044</v>
       </c>
       <c r="R6" t="n">
-        <v>7000864</v>
+        <v>7000989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,6 +1275,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1294,9 +1284,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131244110</v>
       </c>
       <c r="B8" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131244109</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>131244210</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131244190</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57990</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>131244212</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>57718</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244108</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131244213</v>
       </c>
       <c r="B3" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>131244111</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131244211</v>
+        <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>58045</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,50 +1081,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446698</v>
+        <v>447044</v>
       </c>
       <c r="R5" t="n">
-        <v>7000864</v>
+        <v>7000989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,6 +1152,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,9 +1161,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1193,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244216</v>
+        <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>58046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,37 +1202,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447044</v>
+        <v>446698</v>
       </c>
       <c r="R6" t="n">
-        <v>7000989</v>
+        <v>7000864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1286,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1284,19 +1294,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131244110</v>
       </c>
       <c r="B8" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131244109</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>131244210</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131244190</v>
       </c>
       <c r="B15" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>131244212</v>
       </c>
       <c r="B17" t="n">
-        <v>57718</v>
+        <v>57719</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244108</v>
+        <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>91813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446594</v>
+        <v>447044</v>
       </c>
       <c r="R2" t="n">
-        <v>7000953</v>
+        <v>7000989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,23 +755,19 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -785,14 +780,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244213</v>
+        <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>91813</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,28 +811,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447044</v>
+        <v>446673</v>
       </c>
       <c r="R3" t="n">
-        <v>7000989</v>
+        <v>7000892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,6 +880,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -915,9 +910,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244111</v>
+        <v>131244108</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,28 +946,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -977,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446673</v>
+        <v>446594</v>
       </c>
       <c r="R4" t="n">
-        <v>7000892</v>
+        <v>7000953</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,13 +1027,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244189</v>
+        <v>131244217</v>
       </c>
       <c r="B13" t="n">
-        <v>58046</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,50 +2087,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446792</v>
+        <v>447029</v>
       </c>
       <c r="R13" t="n">
-        <v>7001280</v>
+        <v>7000963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2171,12 +2158,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2194,10 +2197,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131244217</v>
+        <v>131244189</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>58046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,37 +2208,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447029</v>
+        <v>446792</v>
       </c>
       <c r="R14" t="n">
-        <v>7000963</v>
+        <v>7001280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2276,28 +2292,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244213</v>
+        <v>131244111</v>
       </c>
       <c r="B2" t="n">
-        <v>91813</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447044</v>
+        <v>446673</v>
       </c>
       <c r="R2" t="n">
-        <v>7000989</v>
+        <v>7000892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +755,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,9 +785,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>91814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,28 +821,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R3" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +890,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,14 +915,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,7 +938,7 @@
         <v>131244108</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131244109</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>131244210</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>131244217</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>131244189</v>
       </c>
       <c r="B14" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131244190</v>
       </c>
       <c r="B15" t="n">
-        <v>57991</v>
+        <v>57992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>131244212</v>
       </c>
       <c r="B17" t="n">
-        <v>57719</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>91814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R2" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +755,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -785,14 +780,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244213</v>
+        <v>131244108</v>
       </c>
       <c r="B3" t="n">
-        <v>91814</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,28 +811,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447044</v>
+        <v>446594</v>
       </c>
       <c r="R3" t="n">
-        <v>7000989</v>
+        <v>7000953</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,19 +881,23 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -915,9 +910,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244108</v>
+        <v>131244111</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,29 +946,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -978,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446594</v>
+        <v>446673</v>
       </c>
       <c r="R4" t="n">
-        <v>7000953</v>
+        <v>7000892</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1017,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,12 +1026,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91814</v>
+        <v>91817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244108</v>
+        <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,29 +811,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -843,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446594</v>
+        <v>446673</v>
       </c>
       <c r="R3" t="n">
-        <v>7000953</v>
+        <v>7000892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +891,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244111</v>
+        <v>131244108</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,28 +946,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -977,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446673</v>
+        <v>446594</v>
       </c>
       <c r="R4" t="n">
-        <v>7000892</v>
+        <v>7000953</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,13 +1027,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
         <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131244110</v>
       </c>
       <c r="B8" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131244109</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>131244210</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244217</v>
+        <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>58050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,37 +2087,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447029</v>
+        <v>446792</v>
       </c>
       <c r="R13" t="n">
-        <v>7000963</v>
+        <v>7001280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,28 +2171,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2197,10 +2194,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131244189</v>
+        <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>58047</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,50 +2205,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446792</v>
+        <v>447029</v>
       </c>
       <c r="R14" t="n">
-        <v>7001280</v>
+        <v>7000963</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,12 +2276,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2318,7 +2318,7 @@
         <v>131244190</v>
       </c>
       <c r="B15" t="n">
-        <v>57992</v>
+        <v>57995</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>131244212</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 46976-2024 artfynd.xlsx
+++ b/artfynd/A 46976-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>131244108</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131244110</v>
       </c>
       <c r="B8" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131244109</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>131244210</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131244190</v>
       </c>
       <c r="B15" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>131244212</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
